--- a/01_analyses_states/Kerala/results/SoIB_summaries.xlsx
+++ b/01_analyses_states/Kerala/results/SoIB_summaries.xlsx
@@ -415,13 +415,13 @@
         <v>0</v>
       </c>
       <c r="C3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D3">
         <v>0</v>
       </c>
       <c r="E3">
-        <v>21.1</v>
+        <v>25</v>
       </c>
     </row>
     <row r="4">
@@ -431,16 +431,16 @@
         </is>
       </c>
       <c r="B4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C4">
         <v>12</v>
       </c>
       <c r="D4">
-        <v>37.5</v>
+        <v>57.1</v>
       </c>
       <c r="E4">
-        <v>63.2</v>
+        <v>60</v>
       </c>
     </row>
     <row r="5">
@@ -450,16 +450,16 @@
         </is>
       </c>
       <c r="B5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C5">
         <v>1</v>
       </c>
       <c r="D5">
-        <v>50</v>
+        <v>28.6</v>
       </c>
       <c r="E5">
-        <v>5.3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
@@ -475,10 +475,10 @@
         <v>2</v>
       </c>
       <c r="D6">
-        <v>12.5</v>
+        <v>14.3</v>
       </c>
       <c r="E6">
-        <v>10.5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7">
@@ -488,10 +488,10 @@
         </is>
       </c>
       <c r="B7">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="C7">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="8">
@@ -501,10 +501,10 @@
         </is>
       </c>
       <c r="B8">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="C8">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
   </sheetData>
@@ -643,7 +643,7 @@
         </is>
       </c>
       <c r="B4">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
   </sheetData>
@@ -680,7 +680,7 @@
         </is>
       </c>
       <c r="B2">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="3">
@@ -690,10 +690,10 @@
         </is>
       </c>
       <c r="B3">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="C3">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4">
@@ -703,10 +703,10 @@
         </is>
       </c>
       <c r="B4">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="C4">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5">

--- a/01_analyses_states/Kerala/results/SoIB_summaries.xlsx
+++ b/01_analyses_states/Kerala/results/SoIB_summaries.xlsx
@@ -396,13 +396,13 @@
         <v>0</v>
       </c>
       <c r="C2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D2">
         <v>0</v>
       </c>
       <c r="E2">
-        <v>3.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -421,7 +421,7 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>17.2</v>
+        <v>25</v>
       </c>
     </row>
     <row r="4">
@@ -434,13 +434,13 @@
         <v>4</v>
       </c>
       <c r="C4">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="D4">
-        <v>44.4</v>
+        <v>57.1</v>
       </c>
       <c r="E4">
-        <v>65.5</v>
+        <v>60</v>
       </c>
     </row>
     <row r="5">
@@ -450,16 +450,16 @@
         </is>
       </c>
       <c r="B5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D5">
-        <v>44.4</v>
+        <v>28.6</v>
       </c>
       <c r="E5">
-        <v>6.9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
@@ -475,10 +475,10 @@
         <v>2</v>
       </c>
       <c r="D6">
-        <v>11.1</v>
+        <v>14.3</v>
       </c>
       <c r="E6">
-        <v>6.9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7">
@@ -488,10 +488,10 @@
         </is>
       </c>
       <c r="B7">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="C7">
-        <v>125</v>
+        <v>137</v>
       </c>
     </row>
     <row r="8">
@@ -501,10 +501,10 @@
         </is>
       </c>
       <c r="B8">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="C8">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
   </sheetData>
@@ -643,7 +643,7 @@
         </is>
       </c>
       <c r="B4">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
   </sheetData>
@@ -680,7 +680,7 @@
         </is>
       </c>
       <c r="B2">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="3">
@@ -690,10 +690,10 @@
         </is>
       </c>
       <c r="B3">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="C3">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4">
@@ -703,10 +703,10 @@
         </is>
       </c>
       <c r="B4">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="C4">
-        <v>29</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5">

--- a/01_analyses_states/Kerala/results/SoIB_summaries.xlsx
+++ b/01_analyses_states/Kerala/results/SoIB_summaries.xlsx
@@ -396,13 +396,13 @@
         <v>0</v>
       </c>
       <c r="C2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D2">
         <v>0</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="3">
@@ -415,13 +415,13 @@
         <v>0</v>
       </c>
       <c r="C3">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="D3">
         <v>0</v>
       </c>
       <c r="E3">
-        <v>25</v>
+        <v>23.3</v>
       </c>
     </row>
     <row r="4">
@@ -431,16 +431,16 @@
         </is>
       </c>
       <c r="B4">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C4">
-        <v>12</v>
+        <v>45</v>
       </c>
       <c r="D4">
-        <v>57.1</v>
+        <v>50</v>
       </c>
       <c r="E4">
-        <v>60</v>
+        <v>61.6</v>
       </c>
     </row>
     <row r="5">
@@ -450,16 +450,16 @@
         </is>
       </c>
       <c r="B5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C5">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D5">
-        <v>28.6</v>
+        <v>25</v>
       </c>
       <c r="E5">
-        <v>5</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="6">
@@ -469,16 +469,16 @@
         </is>
       </c>
       <c r="B6">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C6">
         <v>2</v>
       </c>
       <c r="D6">
-        <v>14.3</v>
+        <v>25</v>
       </c>
       <c r="E6">
-        <v>10</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="7">
@@ -488,10 +488,10 @@
         </is>
       </c>
       <c r="B7">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="C7">
-        <v>137</v>
+        <v>83</v>
       </c>
     </row>
     <row r="8">
@@ -501,10 +501,10 @@
         </is>
       </c>
       <c r="B8">
-        <v>376</v>
+        <v>369</v>
       </c>
       <c r="C8">
-        <v>268</v>
+        <v>261</v>
       </c>
     </row>
   </sheetData>
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B3">
-        <v>286</v>
+        <v>387</v>
       </c>
     </row>
     <row r="4">
@@ -643,7 +643,7 @@
         </is>
       </c>
       <c r="B4">
-        <v>553</v>
+        <v>441</v>
       </c>
     </row>
   </sheetData>
@@ -680,7 +680,7 @@
         </is>
       </c>
       <c r="B2">
-        <v>425</v>
+        <v>417</v>
       </c>
     </row>
     <row r="3">
@@ -690,10 +690,10 @@
         </is>
       </c>
       <c r="B3">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C3">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4">
@@ -703,10 +703,10 @@
         </is>
       </c>
       <c r="B4">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C4">
-        <v>20</v>
+        <v>73</v>
       </c>
     </row>
     <row r="5">
@@ -763,16 +763,16 @@
         </is>
       </c>
       <c r="B2">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="C2">
-        <v>66</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="D2">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="E2">
-        <v>77.3</v>
+        <v>77.40000000000001</v>
       </c>
     </row>
     <row r="3">
@@ -782,16 +782,16 @@
         </is>
       </c>
       <c r="B3">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="C3">
-        <v>34</v>
+        <v>30.1</v>
       </c>
       <c r="D3">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E3">
-        <v>22.7</v>
+        <v>22.6</v>
       </c>
     </row>
   </sheetData>
